--- a/results/GLCM/Unet/POLYP_CLAHE/POLYP_CLAHE_Unet_GLCM.xlsx
+++ b/results/GLCM/Unet/POLYP_CLAHE/POLYP_CLAHE_Unet_GLCM.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[('correlation', 0.2909484716804597), ('autocorrelation', 0.3558890548496623), ('MCC', 0.5232773537245173), ('IDM', 0.7830925962687819), ('IMC2', 0.8276207430407964), ('entropy', 0.9389230595849698), ('diff_entropy', 0.9582461136052527), ('contrast', 1.0270562684709308), ('IMC1', 1.225158740709894), ('ASM', 1.5086539695721446), ('sum_average', 1.5525509548121854), ('variance', 1.6241797204572506), ('sum_entropy', 1.6491469203417806)]</t>
+          <t>[('correlation', 0.29806679167187583), ('autocorrelation', 0.3405862351907818), ('MCC', 0.5775906033212177), ('IMC2', 0.7693391449018427), ('IDM', 0.7695976503707213), ('entropy', 0.8898383653947879), ('diff_entropy', 0.9103529844414577), ('contrast', 0.9979800616081453), ('IMC1', 1.226426526210656), ('ASM', 1.4337617783380128), ('sum_average', 1.4773939926168203), ('variance', 1.6000428415938626), ('sum_entropy', 1.625148352393181)]</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[('autocorrelation', 0.2932804460276465), ('IMC2', 0.40450247524986555), ('entropy', 0.5565241193081407), ('diff_entropy', 0.5731546355238935), ('IDM', 0.6226776361353141), ('correlation', 0.6444621672545243), ('MCC', 0.8153953319117273), ('IMC1', 0.9970776087926445), ('contrast', 1.1207955416812196), ('variance', 1.2555519888252178), ('sum_average', 1.29764409911119), ('ASM', 1.374298748253223), ('sum_entropy', 1.3884391755233305)]</t>
+          <t>[('autocorrelation', 0.3301333960451397), ('IMC2', 0.43236314310777707), ('entropy', 0.564876467940141), ('diff_entropy', 0.5662537966672716), ('IDM', 0.5939860820014797), ('correlation', 0.6351584634436394), ('MCC', 0.841467289168791), ('IMC1', 0.9595917049945502), ('contrast', 1.069294472448673), ('sum_average', 1.282010844551646), ('ASM', 1.2879282784058677), ('variance', 1.3194407835474735), ('sum_entropy', 1.4359796031860022)]</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[('autocorrelation', 0.16596215438613202), ('IMC2', 0.3486845571813957), ('entropy', 0.3649084562607439), ('diff_entropy', 0.38434482080261323), ('IDM', 0.516689025341903), ('MCC', 0.662210473928212), ('correlation', 0.7446354565210203), ('IMC1', 0.9048721818830101), ('variance', 0.9502827818035421), ('sum_average', 1.106915762790455), ('sum_entropy', 1.1558862282758287), ('ASM', 1.1746445836180432), ('contrast', 1.4393600411945724)]</t>
+          <t>[('autocorrelation', 0.17274721321601305), ('IMC2', 0.33517815105013876), ('entropy', 0.41043360954669766), ('diff_entropy', 0.44874342212229423), ('IDM', 0.5874438862998144), ('MCC', 0.6492646518428041), ('correlation', 0.7493552200892599), ('IMC1', 0.9738931921353997), ('variance', 0.9805619359862032), ('sum_average', 1.162042572141103), ('sum_entropy', 1.1837269572847546), ('ASM', 1.3461232663662326), ('contrast', 1.4045537635921992)]</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[('autocorrelation', 0.056741918762442896), ('MCC', 0.2377500709933954), ('entropy', 0.2864682730972491), ('IMC2', 0.2974973257523184), ('diff_entropy', 0.3540016519482917), ('IDM', 0.5122430244900521), ('variance', 0.7671241183011295), ('correlation', 0.7714531435217072), ('IMC1', 0.8703734015960242), ('sum_entropy', 1.0128525856449577), ('sum_average', 1.062503089775184), ('ASM', 1.2153468666650493), ('contrast', 1.58034174596866)]</t>
+          <t>[('autocorrelation', 0.05893420837317531), ('MCC', 0.24043159411633447), ('entropy', 0.29499959099579404), ('IMC2', 0.3018500900860165), ('diff_entropy', 0.36035877049560383), ('IDM', 0.5614563284644821), ('correlation', 0.773208393465346), ('variance', 0.7799778317629572), ('IMC1', 0.9297202072318876), ('sum_entropy', 1.0244801531969507), ('sum_average', 1.0515764365291482), ('ASM', 1.2399166782026354), ('contrast', 1.5794117324830637)]</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[('autocorrelation', 0.06370863765850744), ('MCC', 0.2309532294623733), ('IMC2', 0.3500308659175741), ('entropy', 0.4244849083057875), ('diff_entropy', 0.5874579324010167), ('variance', 0.6565290450550647), ('IDM', 0.6821485616170304), ('correlation', 0.7726609704809566), ('sum_entropy', 0.8708446872511584), ('sum_average', 1.0642246292254716), ('IMC1', 1.0962514422790974), ('ASM', 1.42003046690577), ('contrast', 1.5897088521437361)]</t>
+          <t>[('autocorrelation', 0.06037909337126952), ('MCC', 0.25297364219981955), ('IMC2', 0.34787426793621967), ('entropy', 0.42201057011862686), ('diff_entropy', 0.5880636457506336), ('variance', 0.6061672108601848), ('IDM', 0.6929269175766284), ('correlation', 0.7386930105404569), ('sum_entropy', 0.7890718393299965), ('sum_average', 1.022019942878473), ('IMC1', 1.1146733141005036), ('ASM', 1.4078186981903706), ('contrast', 1.6152070627251462)]</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[('correlation', 0.022081544056489256), ('autocorrelation', 0.05915580148863497), ('MCC', 0.23403422791840983), ('IMC2', 0.5820405146262428), ('entropy', 0.5841127050450271), ('diff_entropy', 0.6325920679699479), ('IDM', 0.6845111162747737), ('sum_average', 1.200144623032403), ('sum_entropy', 1.2162047146736015), ('variance', 1.2167918625387695), ('IMC1', 1.2362527212898442), ('contrast', 1.3875304156915758), ('ASM', 1.4195979158514573)]</t>
+          <t>[('correlation', 0.019669014867639313), ('autocorrelation', 0.034232635653171965), ('MCC', 0.22464092979060246), ('IMC2', 0.5236899677580434), ('entropy', 0.553519059791101), ('diff_entropy', 0.6152787466247034), ('IDM', 0.7930876116816812), ('sum_entropy', 1.1251912298117972), ('variance', 1.1278563926045369), ('sum_average', 1.2906262350930924), ('IMC1', 1.372690845170263), ('contrast', 1.4246678772473322), ('ASM', 1.704995011565636)]</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[('correlation', 0.09164133414263245), ('autocorrelation', 0.09626634448975452), ('IMC2', 0.3785400413057615), ('MCC', 0.38022159026752045), ('entropy', 0.5086722449988598), ('diff_entropy', 0.5133415693294355), ('IDM', 0.5525529450470177), ('contrast', 0.698821502729112), ('IMC1', 0.9775230884447821), ('variance', 1.1407440658564618), ('sum_average', 1.1535797811411448), ('sum_entropy', 1.1561680077502716), ('ASM', 1.2903166797777927)]</t>
+          <t>[('autocorrelation', 0.06329353093237808), ('correlation', 0.0653998417164615), ('MCC', 0.2423927349691698), ('IMC2', 0.27605666915800553), ('entropy', 0.4399799599488527), ('diff_entropy', 0.45324581846756284), ('IDM', 0.6169601422017181), ('contrast', 0.6524605576943063), ('variance', 1.0573745054786468), ('sum_entropy', 1.0684971997303678), ('IMC1', 1.1081425586874487), ('sum_average', 1.2156562792258727), ('ASM', 1.592670268247381)]</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[('autocorrelation', 0.07505010065388887), ('correlation', 0.18145595876824788), ('MCC', 0.3130502603968696), ('IMC2', 0.3164577173191465), ('entropy', 0.4810843689646538), ('diff_entropy', 0.5184580810389474), ('IDM', 0.6323710742306863), ('variance', 0.8380029289314417), ('contrast', 0.8688061093419199), ('sum_entropy', 0.89348352987213), ('IMC1', 0.9794047340095), ('sum_average', 1.179577733588219), ('ASM', 1.5343325283178668)]</t>
+          <t>[('autocorrelation', 0.07056586617332665), ('correlation', 0.16602469921910074), ('MCC', 0.24494660347290698), ('IMC2', 0.3081853099667311), ('entropy', 0.4929366688456713), ('diff_entropy', 0.5335487505138515), ('IDM', 0.6313676532302996), ('variance', 0.7711403233382725), ('sum_entropy', 0.8260651811369055), ('contrast', 0.8410948461629526), ('IMC1', 0.9921841380794183), ('sum_average', 1.1872825203882407), ('ASM', 1.5885142811406001)]</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[('autocorrelation', 0.04164809967614781), ('MCC', 0.12499445138403001), ('correlation', 0.31316177255917216), ('IMC2', 0.31479258714603764), ('entropy', 0.45910248020992717), ('diff_entropy', 0.560628477519708), ('variance', 0.5918109845166875), ('IDM', 0.6456457547247012), ('sum_entropy', 0.670305211173287), ('IMC1', 1.0362659137303734), ('sum_average', 1.069496361991544), ('contrast', 1.375305751293527), ('ASM', 1.5459991059743043)]</t>
+          <t>[('autocorrelation', 0.03361006013219353), ('MCC', 0.1442594442655099), ('IMC2', 0.2708163023333757), ('correlation', 0.30141284431048554), ('entropy', 0.4557052936175229), ('variance', 0.5229820847415327), ('diff_entropy', 0.5673839589928346), ('sum_entropy', 0.6027365972364965), ('IDM', 0.6168694909841462), ('IMC1', 0.9753751348665278), ('sum_average', 1.087002071233109), ('contrast', 1.417882715328027), ('ASM', 1.6410670541464678)]</t>
         </is>
       </c>
     </row>
